--- a/data/trans_orig/P19-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2007</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>42128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67179</t>
+          <t>68026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47381</t>
+          <t>46390</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74197</t>
+          <t>74379</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95614</t>
+          <t>96427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133640</t>
+          <t>133726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>205831</t>
+          <t>204984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231310</t>
+          <t>230882</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186641</t>
+          <t>186459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>213457</t>
+          <t>214448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>400208</t>
+          <t>400122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>438234</t>
+          <t>437421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122237</t>
+          <t>122699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>163815</t>
+          <t>164042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153940</t>
+          <t>155699</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>196426</t>
+          <t>196735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>286017</t>
+          <t>289095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>347889</t>
+          <t>347620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329260</t>
+          <t>329033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370838</t>
+          <t>370376</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306598</t>
+          <t>306289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349084</t>
+          <t>347325</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>648210</t>
+          <t>648479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710082</t>
+          <t>707004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56588</t>
+          <t>57992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87209</t>
+          <t>87935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79638</t>
+          <t>80335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111318</t>
+          <t>113611</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145385</t>
+          <t>146732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188848</t>
+          <t>190636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>231637</t>
+          <t>230911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262258</t>
+          <t>260854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224094</t>
+          <t>221801</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255774</t>
+          <t>255077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>465410</t>
+          <t>463622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>508873</t>
+          <t>507526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78689</t>
+          <t>78493</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112097</t>
+          <t>110905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105715</t>
+          <t>104610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>140794</t>
+          <t>140605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193917</t>
+          <t>193775</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240399</t>
+          <t>242736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246574</t>
+          <t>247766</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>279982</t>
+          <t>280178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230662</t>
+          <t>230851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>265741</t>
+          <t>266846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>489728</t>
+          <t>487391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>536210</t>
+          <t>536352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55354</t>
+          <t>54863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81573</t>
+          <t>81074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47956</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74529</t>
+          <t>74052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109266</t>
+          <t>108346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147650</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121735</t>
+          <t>122234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147954</t>
+          <t>148445</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133139</t>
+          <t>133616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159712</t>
+          <t>160544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263326</t>
+          <t>264656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301710</t>
+          <t>302630</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41072</t>
+          <t>42239</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67068</t>
+          <t>66498</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80009</t>
+          <t>78571</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111702</t>
+          <t>110342</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129396</t>
+          <t>129219</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169966</t>
+          <t>171409</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>203743</t>
+          <t>204313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229739</t>
+          <t>228572</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>166442</t>
+          <t>167802</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>198135</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>378989</t>
+          <t>377546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>419559</t>
+          <t>419736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>154882</t>
+          <t>154661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201009</t>
+          <t>200287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>217140</t>
+          <t>218517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>267597</t>
+          <t>266193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>383773</t>
+          <t>388838</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>452371</t>
+          <t>457140</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>413106</t>
+          <t>413828</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>459233</t>
+          <t>459454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>370622</t>
+          <t>372026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>421079</t>
+          <t>419702</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>799963</t>
+          <t>795194</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>868561</t>
+          <t>863496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>68,95%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133360</t>
+          <t>132132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177030</t>
+          <t>175374</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>184802</t>
+          <t>183748</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>235083</t>
+          <t>235629</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>329181</t>
+          <t>330332</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>398078</t>
+          <t>398765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>566765</t>
+          <t>568421</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>610435</t>
+          <t>611663</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>548428</t>
+          <t>547882</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>598709</t>
+          <t>599763</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1129228</t>
+          <t>1128541</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1198125</t>
+          <t>1196974</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>761136</t>
+          <t>765770</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>862782</t>
+          <t>869320</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1006886</t>
+          <t>1006060</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1110122</t>
+          <t>1115428</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1798612</t>
+          <t>1794572</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1942870</t>
+          <t>1949930</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2412849</t>
+          <t>2406311</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2514495</t>
+          <t>2509861</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2268150</t>
+          <t>2262844</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2371386</t>
+          <t>2372212</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4711034</t>
+          <t>4703974</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4855292</t>
+          <t>4859332</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2012</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60517</t>
+          <t>60254</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90619</t>
+          <t>91727</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61957</t>
+          <t>61012</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93654</t>
+          <t>94855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131298</t>
+          <t>131992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176638</t>
+          <t>177016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202969</t>
+          <t>201861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233071</t>
+          <t>233334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>193591</t>
+          <t>192390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>225288</t>
+          <t>226233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>404195</t>
+          <t>403817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>449535</t>
+          <t>448841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,28%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106532</t>
+          <t>106246</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145058</t>
+          <t>145069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112865</t>
+          <t>114063</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>154036</t>
+          <t>152635</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232288</t>
+          <t>229959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289033</t>
+          <t>286794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360469</t>
+          <t>360458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>398995</t>
+          <t>399281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>369729</t>
+          <t>371130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>410900</t>
+          <t>409702</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>740259</t>
+          <t>742498</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>797004</t>
+          <t>799333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60763</t>
+          <t>59672</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91271</t>
+          <t>91585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105716</t>
+          <t>104617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142547</t>
+          <t>141232</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170879</t>
+          <t>175683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223461</t>
+          <t>221668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>231412</t>
+          <t>231098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>261920</t>
+          <t>263011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198473</t>
+          <t>199788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>235304</t>
+          <t>236403</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>440242</t>
+          <t>442035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>492824</t>
+          <t>488020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83612</t>
+          <t>83833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118328</t>
+          <t>119560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84444</t>
+          <t>82889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118720</t>
+          <t>117649</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176226</t>
+          <t>178917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227743</t>
+          <t>231456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>255654</t>
+          <t>254422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>290370</t>
+          <t>290149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>270231</t>
+          <t>271302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304507</t>
+          <t>306062</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535190</t>
+          <t>531477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>586707</t>
+          <t>584016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28909</t>
+          <t>30848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52998</t>
+          <t>54078</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57736</t>
+          <t>58018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86390</t>
+          <t>84888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96515</t>
+          <t>94849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132770</t>
+          <t>132779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159620</t>
+          <t>158540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183709</t>
+          <t>181770</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132237</t>
+          <t>133739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160891</t>
+          <t>160609</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298475</t>
+          <t>298466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>334730</t>
+          <t>336396</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68974</t>
+          <t>68704</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100343</t>
+          <t>101199</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69650</t>
+          <t>69178</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>145726</t>
+          <t>145845</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>191260</t>
+          <t>190797</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>173638</t>
+          <t>172782</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205007</t>
+          <t>205277</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>178599</t>
+          <t>179193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>210381</t>
+          <t>210853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>362752</t>
+          <t>363215</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>408286</t>
+          <t>408167</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,67%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139556</t>
+          <t>140173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185744</t>
+          <t>186703</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208938</t>
+          <t>206896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>258767</t>
+          <t>258005</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>359398</t>
+          <t>363396</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>431786</t>
+          <t>431421</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>477044</t>
+          <t>476085</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>523232</t>
+          <t>522615</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>435086</t>
+          <t>435848</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>484915</t>
+          <t>486957</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>924855</t>
+          <t>925220</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>997243</t>
+          <t>993245</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>159969</t>
+          <t>159623</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>207479</t>
+          <t>207568</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>227068</t>
+          <t>226641</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>282570</t>
+          <t>281384</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>404392</t>
+          <t>403531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>480719</t>
+          <t>474275</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>571619</t>
+          <t>571530</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>619129</t>
+          <t>619475</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>541283</t>
+          <t>542469</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>596785</t>
+          <t>597212</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1122232</t>
+          <t>1128676</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1198559</t>
+          <t>1199420</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>793371</t>
+          <t>795892</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>893185</t>
+          <t>897514</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1026159</t>
+          <t>1018088</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1139075</t>
+          <t>1129440</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1849388</t>
+          <t>1844792</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2002245</t>
+          <t>1998460</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2531081</t>
+          <t>2526752</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2630895</t>
+          <t>2628374</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2418270</t>
+          <t>2427905</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2531186</t>
+          <t>2539257</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4979365</t>
+          <t>4983150</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5132222</t>
+          <t>5136818</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2016</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71125</t>
+          <t>73403</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105120</t>
+          <t>107065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84958</t>
+          <t>83022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118420</t>
+          <t>115344</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166466</t>
+          <t>166897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>214377</t>
+          <t>214189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>188641</t>
+          <t>186696</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222636</t>
+          <t>220358</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170283</t>
+          <t>173359</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203745</t>
+          <t>205681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368087</t>
+          <t>368275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415998</t>
+          <t>415567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,35%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124163</t>
+          <t>121842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>163540</t>
+          <t>163059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148855</t>
+          <t>144663</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191442</t>
+          <t>188742</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>285720</t>
+          <t>280215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>342050</t>
+          <t>342497</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>339035</t>
+          <t>339516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>378412</t>
+          <t>380733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331642</t>
+          <t>334342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374229</t>
+          <t>378421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683609</t>
+          <t>683162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>739939</t>
+          <t>745444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80288</t>
+          <t>79729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111461</t>
+          <t>111041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87975</t>
+          <t>87562</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123644</t>
+          <t>122927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176599</t>
+          <t>178337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224516</t>
+          <t>223663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>207104</t>
+          <t>207524</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>238277</t>
+          <t>238836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>212665</t>
+          <t>213382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248334</t>
+          <t>248747</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>430358</t>
+          <t>431211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>478275</t>
+          <t>476537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,77%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95317</t>
+          <t>95262</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132017</t>
+          <t>133700</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127301</t>
+          <t>126520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167569</t>
+          <t>167936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>234166</t>
+          <t>235007</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>289005</t>
+          <t>288190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237947</t>
+          <t>236264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274647</t>
+          <t>274702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219714</t>
+          <t>219347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259982</t>
+          <t>260763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>468242</t>
+          <t>469057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>523081</t>
+          <t>522240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25172</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46622</t>
+          <t>47328</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43857</t>
+          <t>44387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70159</t>
+          <t>68931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75503</t>
+          <t>75039</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108724</t>
+          <t>109165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164599</t>
+          <t>163893</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186049</t>
+          <t>186257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148428</t>
+          <t>149656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174730</t>
+          <t>174200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>321084</t>
+          <t>320643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>354305</t>
+          <t>354769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77927</t>
+          <t>78853</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109566</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>98241</t>
+          <t>96320</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>128339</t>
+          <t>131387</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>183913</t>
+          <t>182149</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>229109</t>
+          <t>228300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153557</t>
+          <t>154116</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185196</t>
+          <t>184270</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144776</t>
+          <t>141728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>174874</t>
+          <t>176795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>307129</t>
+          <t>307938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>352325</t>
+          <t>354089</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>160679</t>
+          <t>161052</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>208172</t>
+          <t>210234</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>228820</t>
+          <t>233167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>281760</t>
+          <t>283174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>406032</t>
+          <t>407344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>476224</t>
+          <t>478724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>448386</t>
+          <t>446324</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>495879</t>
+          <t>495506</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>409534</t>
+          <t>408120</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>462474</t>
+          <t>458127</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>871628</t>
+          <t>869128</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>941820</t>
+          <t>940508</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>206452</t>
+          <t>205825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>258137</t>
+          <t>259022</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>250957</t>
+          <t>248468</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>308444</t>
+          <t>303602</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>470179</t>
+          <t>475900</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>548942</t>
+          <t>553472</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>520446</t>
+          <t>519561</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>572131</t>
+          <t>572758</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>517723</t>
+          <t>522565</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>575210</t>
+          <t>577699</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1055808</t>
+          <t>1051278</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1134571</t>
+          <t>1128850</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>927665</t>
+          <t>934257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1038411</t>
+          <t>1035721</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1165881</t>
+          <t>1168344</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1279347</t>
+          <t>1281496</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2120052</t>
+          <t>2131619</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2285927</t>
+          <t>2290065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2355939</t>
+          <t>2358629</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2466685</t>
+          <t>2460093</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2265195</t>
+          <t>2263046</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2378661</t>
+          <t>2376198</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4652965</t>
+          <t>4648827</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4818840</t>
+          <t>4807273</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2023</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2023 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95459</t>
+          <t>93488</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136934</t>
+          <t>137152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100552</t>
+          <t>100347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128179</t>
+          <t>129082</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204195</t>
+          <t>206042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256994</t>
+          <t>256593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174509</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215984</t>
+          <t>217955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>160173</t>
+          <t>159270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>187800</t>
+          <t>188005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>342801</t>
+          <t>343202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>395600</t>
+          <t>393753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,65%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103317</t>
+          <t>104312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154023</t>
+          <t>154991</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121558</t>
+          <t>121380</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157623</t>
+          <t>157924</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>235265</t>
+          <t>234607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>299173</t>
+          <t>297693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363490</t>
+          <t>362522</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414196</t>
+          <t>413201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354402</t>
+          <t>354101</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>390467</t>
+          <t>390645</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730365</t>
+          <t>731845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>794273</t>
+          <t>794931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51811</t>
+          <t>51039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79467</t>
+          <t>78790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91954</t>
+          <t>91283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121381</t>
+          <t>121360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151469</t>
+          <t>150384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191941</t>
+          <t>191507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234158</t>
+          <t>234835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>261814</t>
+          <t>262586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226525</t>
+          <t>226546</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255952</t>
+          <t>256623</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>469590</t>
+          <t>470024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>510062</t>
+          <t>511147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100444</t>
+          <t>98144</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>143973</t>
+          <t>143198</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118062</t>
+          <t>121977</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>250514</t>
+          <t>249244</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242219</t>
+          <t>239477</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>372033</t>
+          <t>375408</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,9%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168013</t>
+          <t>168788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211542</t>
+          <t>213842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221174</t>
+          <t>222444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>353626</t>
+          <t>349711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411641</t>
+          <t>408266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>541455</t>
+          <t>544197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15627</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31027</t>
+          <t>29590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30700</t>
+          <t>30146</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45762</t>
+          <t>46087</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49581</t>
+          <t>48767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70059</t>
+          <t>70103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147715</t>
+          <t>149152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163115</t>
+          <t>163971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160349</t>
+          <t>160024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175411</t>
+          <t>175965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>314794</t>
+          <t>314750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335272</t>
+          <t>336086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53133</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>78242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62146</t>
+          <t>62162</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84429</t>
+          <t>85358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123099</t>
+          <t>121336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>156923</t>
+          <t>157903</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>189625</t>
+          <t>191394</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216503</t>
+          <t>217776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>172627</t>
+          <t>171698</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>194910</t>
+          <t>194894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>369769</t>
+          <t>368789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>403593</t>
+          <t>405356</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>184469</t>
+          <t>186229</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>238472</t>
+          <t>241136</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129569</t>
+          <t>131167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>339392</t>
+          <t>340845</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>297174</t>
+          <t>269318</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>554029</t>
+          <t>549224</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>373021</t>
+          <t>370357</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>427024</t>
+          <t>425264</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>496876</t>
+          <t>495423</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>706699</t>
+          <t>705101</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>893731</t>
+          <t>898536</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1150586</t>
+          <t>1178442</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58400</t>
+          <t>62270</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196451</t>
+          <t>189371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154587</t>
+          <t>150952</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>192558</t>
+          <t>190214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>182092</t>
+          <t>190939</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>371254</t>
+          <t>372530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>725644</t>
+          <t>732724</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>863695</t>
+          <t>859825</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>517851</t>
+          <t>520195</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>555822</t>
+          <t>559457</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1261250</t>
+          <t>1259974</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1450412</t>
+          <t>1441565</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>650025</t>
+          <t>669893</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>952093</t>
+          <t>947806</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>878391</t>
+          <t>884215</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1189142</t>
+          <t>1187018</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1715635</t>
+          <t>1673995</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2097718</t>
+          <t>2093062</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2484439</t>
+          <t>2488726</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2786507</t>
+          <t>2766639</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2440672</t>
+          <t>2442796</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2751423</t>
+          <t>2745599</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4968628</t>
+          <t>4973284</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5350711</t>
+          <t>5392351</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42128</t>
+          <t>42193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68026</t>
+          <t>68118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46390</t>
+          <t>45188</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74379</t>
+          <t>72480</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96427</t>
+          <t>93653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133726</t>
+          <t>133083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>204984</t>
+          <t>204892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230882</t>
+          <t>230817</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186459</t>
+          <t>188358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>214448</t>
+          <t>215650</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>400122</t>
+          <t>400765</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>437421</t>
+          <t>440195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122699</t>
+          <t>120006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164042</t>
+          <t>163310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155699</t>
+          <t>156023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>196735</t>
+          <t>197561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>289095</t>
+          <t>289044</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>347620</t>
+          <t>350868</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329033</t>
+          <t>329765</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370376</t>
+          <t>373069</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306289</t>
+          <t>305463</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347325</t>
+          <t>347001</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>648479</t>
+          <t>645231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>707004</t>
+          <t>707055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57992</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87935</t>
+          <t>86792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80335</t>
+          <t>79755</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113611</t>
+          <t>112291</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146732</t>
+          <t>143558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190636</t>
+          <t>186938</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230911</t>
+          <t>232054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>260854</t>
+          <t>261877</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221801</t>
+          <t>223121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255077</t>
+          <t>255657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>463622</t>
+          <t>467320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>507526</t>
+          <t>510700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78493</t>
+          <t>78574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110905</t>
+          <t>112081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104610</t>
+          <t>105663</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>140605</t>
+          <t>141188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193775</t>
+          <t>195804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242736</t>
+          <t>244475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>247766</t>
+          <t>246590</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>280178</t>
+          <t>280097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230851</t>
+          <t>230268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>266846</t>
+          <t>265793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>487391</t>
+          <t>485652</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>536352</t>
+          <t>534323</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54863</t>
+          <t>54913</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81074</t>
+          <t>81586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>48082</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74052</t>
+          <t>75650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108346</t>
+          <t>110620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146320</t>
+          <t>146779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122234</t>
+          <t>121722</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148445</t>
+          <t>148395</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133616</t>
+          <t>132018</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160544</t>
+          <t>159586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264656</t>
+          <t>264197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>302630</t>
+          <t>300356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42239</t>
+          <t>41064</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66498</t>
+          <t>67030</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78571</t>
+          <t>80094</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110342</t>
+          <t>111410</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129219</t>
+          <t>128435</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171409</t>
+          <t>169419</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204313</t>
+          <t>203781</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228572</t>
+          <t>229747</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>167802</t>
+          <t>166734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>199573</t>
+          <t>198050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>377546</t>
+          <t>379536</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>419736</t>
+          <t>420520</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,6%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>154661</t>
+          <t>156836</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200287</t>
+          <t>199682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>218517</t>
+          <t>216407</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>266193</t>
+          <t>266712</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>388838</t>
+          <t>387345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>457140</t>
+          <t>456061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>413828</t>
+          <t>414433</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>459454</t>
+          <t>457279</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>372026</t>
+          <t>371507</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>419702</t>
+          <t>421812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>795194</t>
+          <t>796273</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>863496</t>
+          <t>864989</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132132</t>
+          <t>135195</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175374</t>
+          <t>179775</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183748</t>
+          <t>186026</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>235629</t>
+          <t>235231</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>330332</t>
+          <t>331189</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>398765</t>
+          <t>398126</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>568421</t>
+          <t>564020</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>611663</t>
+          <t>608600</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>547882</t>
+          <t>548280</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>599763</t>
+          <t>597485</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1128541</t>
+          <t>1129180</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1196974</t>
+          <t>1196117</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>767116</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>869320</t>
+          <t>869016</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1006060</t>
+          <t>1007614</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1115428</t>
+          <t>1115681</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1794572</t>
+          <t>1806499</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1949930</t>
+          <t>1946168</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2406311</t>
+          <t>2406615</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2509861</t>
+          <t>2508515</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2262844</t>
+          <t>2262591</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2372212</t>
+          <t>2370658</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4703974</t>
+          <t>4707736</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4859332</t>
+          <t>4847405</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60254</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91727</t>
+          <t>91935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61012</t>
+          <t>61349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94855</t>
+          <t>94111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131992</t>
+          <t>132364</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177016</t>
+          <t>175865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>201861</t>
+          <t>201653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233334</t>
+          <t>231667</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192390</t>
+          <t>193134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226233</t>
+          <t>225896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>403817</t>
+          <t>404968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>448841</t>
+          <t>448469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106246</t>
+          <t>104322</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145069</t>
+          <t>145313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114063</t>
+          <t>113430</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152635</t>
+          <t>152927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229959</t>
+          <t>231414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>286794</t>
+          <t>288885</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360458</t>
+          <t>360214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399281</t>
+          <t>401205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371130</t>
+          <t>370838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>409702</t>
+          <t>410335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>742498</t>
+          <t>740407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>799333</t>
+          <t>797878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59672</t>
+          <t>60149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91585</t>
+          <t>91788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104617</t>
+          <t>105918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141232</t>
+          <t>141394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175683</t>
+          <t>173340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221668</t>
+          <t>222561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>231098</t>
+          <t>230895</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263011</t>
+          <t>262534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>199788</t>
+          <t>199626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>236403</t>
+          <t>235102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>442035</t>
+          <t>441142</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>488020</t>
+          <t>490363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83833</t>
+          <t>82231</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119560</t>
+          <t>118138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82889</t>
+          <t>85252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117649</t>
+          <t>120152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>178917</t>
+          <t>177320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231456</t>
+          <t>226378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>254422</t>
+          <t>255844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>290149</t>
+          <t>291751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>271302</t>
+          <t>268799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306062</t>
+          <t>303699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>531477</t>
+          <t>536555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>584016</t>
+          <t>585613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>30026</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54078</t>
+          <t>53698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58018</t>
+          <t>56530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84888</t>
+          <t>84497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94849</t>
+          <t>95659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132779</t>
+          <t>132814</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158540</t>
+          <t>158920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181770</t>
+          <t>182592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133739</t>
+          <t>134130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160609</t>
+          <t>162097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298466</t>
+          <t>298431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336396</t>
+          <t>335586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68704</t>
+          <t>68935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101199</t>
+          <t>101535</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69178</t>
+          <t>71292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100838</t>
+          <t>101646</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>145845</t>
+          <t>148505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>190797</t>
+          <t>193807</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172782</t>
+          <t>172446</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205277</t>
+          <t>205046</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179193</t>
+          <t>178385</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>210853</t>
+          <t>208739</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>363215</t>
+          <t>360205</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>408167</t>
+          <t>405507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140173</t>
+          <t>139428</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>186703</t>
+          <t>187707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>206896</t>
+          <t>207362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>258005</t>
+          <t>263454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>363396</t>
+          <t>361964</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>431421</t>
+          <t>428479</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>476085</t>
+          <t>475081</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>522615</t>
+          <t>523360</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>435848</t>
+          <t>430399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>486957</t>
+          <t>486491</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>925220</t>
+          <t>928162</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>993245</t>
+          <t>994677</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>159623</t>
+          <t>158761</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>207568</t>
+          <t>208340</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>226641</t>
+          <t>229610</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>281384</t>
+          <t>282219</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>403531</t>
+          <t>400496</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>474275</t>
+          <t>473620</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>571530</t>
+          <t>570758</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>619475</t>
+          <t>620337</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>542469</t>
+          <t>541634</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>597212</t>
+          <t>594243</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1128676</t>
+          <t>1129331</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1199420</t>
+          <t>1202455</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,02%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>795892</t>
+          <t>793953</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>897514</t>
+          <t>900175</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1018088</t>
+          <t>1019104</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1129440</t>
+          <t>1132904</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1844792</t>
+          <t>1846546</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1998460</t>
+          <t>2001610</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2526752</t>
+          <t>2524091</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2628374</t>
+          <t>2630313</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2427905</t>
+          <t>2424441</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2539257</t>
+          <t>2538241</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4983150</t>
+          <t>4980000</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5136818</t>
+          <t>5135064</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73403</t>
+          <t>73748</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107065</t>
+          <t>105844</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83022</t>
+          <t>85395</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115344</t>
+          <t>117566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166897</t>
+          <t>165669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>214189</t>
+          <t>213132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>186696</t>
+          <t>187917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220358</t>
+          <t>220013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173359</t>
+          <t>171137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205681</t>
+          <t>203308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368275</t>
+          <t>369332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415567</t>
+          <t>416795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121842</t>
+          <t>121035</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>163059</t>
+          <t>164796</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144663</t>
+          <t>147591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188742</t>
+          <t>191025</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>280215</t>
+          <t>285086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>342497</t>
+          <t>343031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>339516</t>
+          <t>337779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>380733</t>
+          <t>381540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>334342</t>
+          <t>332059</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>378421</t>
+          <t>375493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683162</t>
+          <t>682628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745444</t>
+          <t>740573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79729</t>
+          <t>80076</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111041</t>
+          <t>111467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87562</t>
+          <t>87892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122927</t>
+          <t>122346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178337</t>
+          <t>177070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223663</t>
+          <t>224251</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>207524</t>
+          <t>207098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>238836</t>
+          <t>238489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213382</t>
+          <t>213963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248747</t>
+          <t>248417</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>431211</t>
+          <t>430623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>476537</t>
+          <t>477804</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95262</t>
+          <t>96429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133700</t>
+          <t>133933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126520</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167936</t>
+          <t>166975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>235007</t>
+          <t>235937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>288190</t>
+          <t>288009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236264</t>
+          <t>236031</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274702</t>
+          <t>273535</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219347</t>
+          <t>220308</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>260763</t>
+          <t>259255</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>469057</t>
+          <t>469238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>522240</t>
+          <t>521310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,84%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47328</t>
+          <t>46592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44387</t>
+          <t>45115</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68931</t>
+          <t>69524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75039</t>
+          <t>75254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109165</t>
+          <t>109061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163893</t>
+          <t>164629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186257</t>
+          <t>186367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149656</t>
+          <t>149063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174200</t>
+          <t>173472</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>320643</t>
+          <t>320747</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>354769</t>
+          <t>354554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78853</t>
+          <t>78782</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>111264</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96320</t>
+          <t>96737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131387</t>
+          <t>129874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182149</t>
+          <t>184857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>228300</t>
+          <t>229425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154116</t>
+          <t>151859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>184270</t>
+          <t>184341</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>141728</t>
+          <t>143241</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>176795</t>
+          <t>176378</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>307938</t>
+          <t>306813</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>354089</t>
+          <t>351381</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>161052</t>
+          <t>160582</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210234</t>
+          <t>210779</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>233167</t>
+          <t>231207</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283174</t>
+          <t>280682</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>407344</t>
+          <t>407755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>478724</t>
+          <t>479301</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>446324</t>
+          <t>445779</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>495506</t>
+          <t>495976</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>408120</t>
+          <t>410612</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>458127</t>
+          <t>460087</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>869128</t>
+          <t>868551</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>940508</t>
+          <t>940097</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>205825</t>
+          <t>206327</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>259022</t>
+          <t>257299</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>248468</t>
+          <t>248442</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>303602</t>
+          <t>306964</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>475900</t>
+          <t>470141</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>553472</t>
+          <t>548199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>519561</t>
+          <t>521284</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>572758</t>
+          <t>572256</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>522565</t>
+          <t>519203</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>577699</t>
+          <t>577725</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1051278</t>
+          <t>1056551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1128850</t>
+          <t>1134609</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,7%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>934257</t>
+          <t>939015</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1035721</t>
+          <t>1038925</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1168344</t>
+          <t>1167396</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1281496</t>
+          <t>1283111</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2131619</t>
+          <t>2129771</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2290065</t>
+          <t>2289983</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2358629</t>
+          <t>2355425</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2460093</t>
+          <t>2455335</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2263046</t>
+          <t>2261431</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2376198</t>
+          <t>2377146</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4648827</t>
+          <t>4648909</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4807273</t>
+          <t>4809121</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>116205</t>
+          <t>111142</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93488</t>
+          <t>94601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137152</t>
+          <t>129694</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>114507</t>
+          <t>118810</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100347</t>
+          <t>103458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129082</t>
+          <t>132657</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>230712</t>
+          <t>229952</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206042</t>
+          <t>209460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256593</t>
+          <t>251739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>195238</t>
+          <t>207703</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>189151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>217955</t>
+          <t>224244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>173845</t>
+          <t>196201</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159270</t>
+          <t>182354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>188005</t>
+          <t>211553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>369083</t>
+          <t>403904</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343202</t>
+          <t>382117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>393753</t>
+          <t>424396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,95%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>288352</t>
+          <t>315011</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>288352</t>
+          <t>315011</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>288352</t>
+          <t>315011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>599795</t>
+          <t>633856</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>599795</t>
+          <t>633856</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>599795</t>
+          <t>633856</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>126950</t>
+          <t>125554</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104312</t>
+          <t>101485</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154991</t>
+          <t>151651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>138025</t>
+          <t>145638</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121380</t>
+          <t>127106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157924</t>
+          <t>165218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>264975</t>
+          <t>271191</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>234607</t>
+          <t>239659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>297693</t>
+          <t>303945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>390563</t>
+          <t>404167</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>362522</t>
+          <t>378070</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413201</t>
+          <t>428236</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>374000</t>
+          <t>397770</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354101</t>
+          <t>378190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>390645</t>
+          <t>416302</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>764563</t>
+          <t>801938</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731845</t>
+          <t>769184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>794931</t>
+          <t>833470</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517513</t>
+          <t>529721</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517513</t>
+          <t>529721</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517513</t>
+          <t>529721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512025</t>
+          <t>543408</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512025</t>
+          <t>543408</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512025</t>
+          <t>543408</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029538</t>
+          <t>1073129</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029538</t>
+          <t>1073129</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029538</t>
+          <t>1073129</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64312</t>
+          <t>65149</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>51431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78790</t>
+          <t>77931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>106038</t>
+          <t>108425</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91283</t>
+          <t>94234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121360</t>
+          <t>124315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>170350</t>
+          <t>173573</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150384</t>
+          <t>153692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191507</t>
+          <t>195121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>249313</t>
+          <t>248462</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234835</t>
+          <t>235680</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262586</t>
+          <t>262180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>241868</t>
+          <t>246698</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226546</t>
+          <t>230808</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256623</t>
+          <t>260889</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>491181</t>
+          <t>495160</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>470024</t>
+          <t>473612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>511147</t>
+          <t>515041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>313625</t>
+          <t>313611</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>313625</t>
+          <t>313611</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>313625</t>
+          <t>313611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347906</t>
+          <t>355123</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347906</t>
+          <t>355123</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347906</t>
+          <t>355123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>668733</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>668733</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>668733</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>120505</t>
+          <t>135071</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98144</t>
+          <t>113337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>143198</t>
+          <t>162563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>194989</t>
+          <t>179968</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121977</t>
+          <t>160766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>249244</t>
+          <t>202109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>315494</t>
+          <t>315039</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>239477</t>
+          <t>284712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>375408</t>
+          <t>349134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>191481</t>
+          <t>237488</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168788</t>
+          <t>209996</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213842</t>
+          <t>259222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>276699</t>
+          <t>237447</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222444</t>
+          <t>215306</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349711</t>
+          <t>256649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>468180</t>
+          <t>474935</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408266</t>
+          <t>440840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>544197</t>
+          <t>505262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>372559</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>372559</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>372559</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>471688</t>
+          <t>417415</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>471688</t>
+          <t>417415</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>471688</t>
+          <t>417415</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>783674</t>
+          <t>789974</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>783674</t>
+          <t>789974</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>783674</t>
+          <t>789974</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14771</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29590</t>
+          <t>32192</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36998</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30146</t>
+          <t>31813</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46087</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>58965</t>
+          <t>62868</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>52343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70103</t>
+          <t>74835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>156776</t>
+          <t>181826</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>149152</t>
+          <t>173473</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163971</t>
+          <t>189078</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>169113</t>
+          <t>185536</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160024</t>
+          <t>176782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175965</t>
+          <t>192752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>325888</t>
+          <t>367362</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>314750</t>
+          <t>355395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336086</t>
+          <t>377887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,83%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>206111</t>
+          <t>224565</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>206111</t>
+          <t>224565</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206111</t>
+          <t>224565</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>384853</t>
+          <t>430230</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384853</t>
+          <t>430230</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384853</t>
+          <t>430230</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>65155</t>
+          <t>62688</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51860</t>
+          <t>50255</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78242</t>
+          <t>77457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>73486</t>
+          <t>74608</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62162</t>
+          <t>62268</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85358</t>
+          <t>85788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>138641</t>
+          <t>137297</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121336</t>
+          <t>121328</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157903</t>
+          <t>157669</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>204481</t>
+          <t>208019</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>191394</t>
+          <t>193250</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>217776</t>
+          <t>220452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>183570</t>
+          <t>189142</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>171698</t>
+          <t>177962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>194894</t>
+          <t>201482</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>388051</t>
+          <t>397160</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>368789</t>
+          <t>376788</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>405356</t>
+          <t>413129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>212827</t>
+          <t>244799</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186229</t>
+          <t>217494</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241136</t>
+          <t>275670</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>249001</t>
+          <t>290847</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>131167</t>
+          <t>265440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>340845</t>
+          <t>315137</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>461828</t>
+          <t>535646</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269318</t>
+          <t>499602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>549224</t>
+          <t>578648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>398666</t>
+          <t>460205</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>370357</t>
+          <t>429334</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>425264</t>
+          <t>487510</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>587267</t>
+          <t>464653</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>495423</t>
+          <t>440363</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>705101</t>
+          <t>490060</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>985932</t>
+          <t>924858</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>898536</t>
+          <t>881856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1178442</t>
+          <t>960902</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>65,79%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>611493</t>
+          <t>705004</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>611493</t>
+          <t>705004</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>611493</t>
+          <t>705004</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>836268</t>
+          <t>755500</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>836268</t>
+          <t>755500</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>836268</t>
+          <t>755500</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1447760</t>
+          <t>1460504</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1447760</t>
+          <t>1460504</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1447760</t>
+          <t>1460504</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>134792</t>
+          <t>154873</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62270</t>
+          <t>131980</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>189371</t>
+          <t>180040</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>171190</t>
+          <t>194606</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>150952</t>
+          <t>172637</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>190214</t>
+          <t>217710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>305982</t>
+          <t>349479</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>190939</t>
+          <t>317461</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>372530</t>
+          <t>382469</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>787303</t>
+          <t>635869</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>732724</t>
+          <t>610702</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>859825</t>
+          <t>658762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>539219</t>
+          <t>629691</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>520195</t>
+          <t>606587</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>559457</t>
+          <t>651660</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1326522</t>
+          <t>1265560</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1259974</t>
+          <t>1232570</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1441565</t>
+          <t>1297578</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>922095</t>
+          <t>790742</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>922095</t>
+          <t>790742</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>922095</t>
+          <t>790742</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>710409</t>
+          <t>824297</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>710409</t>
+          <t>824297</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>710409</t>
+          <t>824297</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1632504</t>
+          <t>1615039</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1632504</t>
+          <t>1615039</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1632504</t>
+          <t>1615039</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>862713</t>
+          <t>923114</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>669893</t>
+          <t>865964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>947806</t>
+          <t>978975</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1084234</t>
+          <t>1151931</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>884215</t>
+          <t>1105992</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1187018</t>
+          <t>1205191</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1946946</t>
+          <t>2075045</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1673995</t>
+          <t>1999274</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2093062</t>
+          <t>2152988</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2573819</t>
+          <t>2583741</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2488726</t>
+          <t>2527880</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2766639</t>
+          <t>2640891</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2545580</t>
+          <t>2547137</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2442796</t>
+          <t>2493877</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2745599</t>
+          <t>2593076</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5119400</t>
+          <t>5130878</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4973284</t>
+          <t>5052935</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5392351</t>
+          <t>5206649</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3436532</t>
+          <t>3506855</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3436532</t>
+          <t>3506855</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3436532</t>
+          <t>3506855</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3629814</t>
+          <t>3699068</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3629814</t>
+          <t>3699068</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3629814</t>
+          <t>3699068</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7066346</t>
+          <t>7205923</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7066346</t>
+          <t>7205923</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7066346</t>
+          <t>7205923</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
